--- a/cleaned_data.xlsx
+++ b/cleaned_data.xlsx
@@ -2,21 +2,41 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dharm\OneDrive\Desktop\personal-finance-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A1F8B9-67EC-4C10-A106-744D0FA8BE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F35805-1A61-4114-A181-C7AAC5344B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="PivotTable1" sheetId="2" r:id="rId2"/>
+    <sheet name="PivotTable2" sheetId="3" r:id="rId3"/>
+    <sheet name="PivotTable3" sheetId="4" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="6" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_Category">#N/A</definedName>
+    <definedName name="Slicer_Months__Date">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="7" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId7"/>
+        <x14:slicerCache r:id="rId8"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -34,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -158,12 +178,60 @@
   <si>
     <t>Flow</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Key Insights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food category contributes the highest share of expenses  </t>
+  </si>
+  <si>
+    <t>Total income is higher than expenses, indicating savings</t>
+  </si>
+  <si>
+    <t>Spending is consistent across months</t>
+  </si>
+  <si>
+    <t>Shopping and entertainment are major expense areas</t>
+  </si>
+  <si>
+    <t>Total Expense</t>
+  </si>
+  <si>
+    <t>Savings</t>
+  </si>
+  <si>
+    <t>Total Income</t>
+  </si>
+  <si>
+    <t>Personal Finance Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Finance Analysis &amp; Insights </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,16 +239,81 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -188,11 +321,145 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -201,8 +468,65 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
+    <cellStyle name="Accent5" xfId="2" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -223,6 +547,5306 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[cleaned_data.xlsx]PivotTable1!PivotTable1</c:name>
+    <c:fmtId val="13"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTable1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-505D-45D3-A364-94D62DE91B6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-505D-45D3-A364-94D62DE91B6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-505D-45D3-A364-94D62DE91B6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-505D-45D3-A364-94D62DE91B6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-505D-45D3-A364-94D62DE91B6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-505D-45D3-A364-94D62DE91B6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTable1!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Bills</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Entertainment</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Food</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Income</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shopping</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Transport</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTable1!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5299</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2687</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8600</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>930</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-505D-45D3-A364-94D62DE91B6C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[cleaned_data.xlsx]PivotTable3!PivotTable3</c:name>
+    <c:fmtId val="13"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10458092738407698"/>
+          <c:y val="0.13786818314377369"/>
+          <c:w val="0.67671062992125985"/>
+          <c:h val="0.65853091280256637"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTable3!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Expense</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTable3!$A$5:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTable3!$B$5:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>17867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6649</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B3FE-496C-A3D8-065EF9785E43}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PivotTable3!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Income</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PivotTable3!$A$5:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PivotTable3!$C$5:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-B3FE-496C-A3D8-065EF9785E43}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="104842816"/>
+        <c:axId val="104861056"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="104842816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="104861056"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="104861056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="104842816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="348">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3364</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>164123</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>11723</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95BB68D3-9067-0C77-B3EF-09AC9F54388C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>161380</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>168441</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>725785</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>31315</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B517AC7D-8704-19C4-1B90-2724402A3560}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>10438</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19522</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>344466</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>177451</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Category 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEA7D531-6A69-475D-99DA-5E82C16B9C3E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr>
+              <a:graphicFrameLocks/>
+            </xdr:cNvGraphicFramePr>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Category 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2448838" y="1355953"/>
+              <a:ext cx="6945843" cy="1799160"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>354904</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12758</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>167013</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Months (Date) 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{291D3904-301E-4CFF-97B6-ED67DE1194EE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Months (Date) 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9405119" y="1349189"/>
+              <a:ext cx="3501989" cy="1795486"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="gaytri dharmatti" refreshedDate="46129.565399305553" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="44" xr:uid="{6FA8EF30-DF20-4B25-92B1-D755AF1FF8C5}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Date" numFmtId="16">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-01T00:00:00" maxDate="2026-02-14T00:00:00" count="44">
+        <d v="2026-01-01T00:00:00"/>
+        <d v="2026-01-02T00:00:00"/>
+        <d v="2026-01-03T00:00:00"/>
+        <d v="2026-01-04T00:00:00"/>
+        <d v="2026-01-05T00:00:00"/>
+        <d v="2026-01-06T00:00:00"/>
+        <d v="2026-01-07T00:00:00"/>
+        <d v="2026-01-08T00:00:00"/>
+        <d v="2026-01-09T00:00:00"/>
+        <d v="2026-01-10T00:00:00"/>
+        <d v="2026-01-11T00:00:00"/>
+        <d v="2026-01-12T00:00:00"/>
+        <d v="2026-01-13T00:00:00"/>
+        <d v="2026-01-14T00:00:00"/>
+        <d v="2026-01-15T00:00:00"/>
+        <d v="2026-01-16T00:00:00"/>
+        <d v="2026-01-17T00:00:00"/>
+        <d v="2026-01-18T00:00:00"/>
+        <d v="2026-01-19T00:00:00"/>
+        <d v="2026-01-20T00:00:00"/>
+        <d v="2026-01-21T00:00:00"/>
+        <d v="2026-01-22T00:00:00"/>
+        <d v="2026-01-23T00:00:00"/>
+        <d v="2026-01-24T00:00:00"/>
+        <d v="2026-01-25T00:00:00"/>
+        <d v="2026-01-26T00:00:00"/>
+        <d v="2026-01-27T00:00:00"/>
+        <d v="2026-01-28T00:00:00"/>
+        <d v="2026-01-29T00:00:00"/>
+        <d v="2026-01-30T00:00:00"/>
+        <d v="2026-01-31T00:00:00"/>
+        <d v="2026-02-01T00:00:00"/>
+        <d v="2026-02-02T00:00:00"/>
+        <d v="2026-02-03T00:00:00"/>
+        <d v="2026-02-04T00:00:00"/>
+        <d v="2026-02-05T00:00:00"/>
+        <d v="2026-02-06T00:00:00"/>
+        <d v="2026-02-07T00:00:00"/>
+        <d v="2026-02-08T00:00:00"/>
+        <d v="2026-02-09T00:00:00"/>
+        <d v="2026-02-10T00:00:00"/>
+        <d v="2026-02-11T00:00:00"/>
+        <d v="2026-02-12T00:00:00"/>
+        <d v="2026-02-13T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="8"/>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Income"/>
+        <s v="Food"/>
+        <s v="Transport"/>
+        <s v="Bills"/>
+        <s v="Entertainment"/>
+        <s v="Shopping"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sub-Category" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Amount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="15000"/>
+    </cacheField>
+    <cacheField name="Type" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Income"/>
+        <s v="Expense"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Payment Mode" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Flow" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Days (Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="days" startDate="2026-01-01T00:00:00" endDate="2026-02-14T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;01-01-2026"/>
+          <s v="01-Jan"/>
+          <s v="02-Jan"/>
+          <s v="03-Jan"/>
+          <s v="04-Jan"/>
+          <s v="05-Jan"/>
+          <s v="06-Jan"/>
+          <s v="07-Jan"/>
+          <s v="08-Jan"/>
+          <s v="09-Jan"/>
+          <s v="10-Jan"/>
+          <s v="11-Jan"/>
+          <s v="12-Jan"/>
+          <s v="13-Jan"/>
+          <s v="14-Jan"/>
+          <s v="15-Jan"/>
+          <s v="16-Jan"/>
+          <s v="17-Jan"/>
+          <s v="18-Jan"/>
+          <s v="19-Jan"/>
+          <s v="20-Jan"/>
+          <s v="21-Jan"/>
+          <s v="22-Jan"/>
+          <s v="23-Jan"/>
+          <s v="24-Jan"/>
+          <s v="25-Jan"/>
+          <s v="26-Jan"/>
+          <s v="27-Jan"/>
+          <s v="28-Jan"/>
+          <s v="29-Jan"/>
+          <s v="30-Jan"/>
+          <s v="31-Jan"/>
+          <s v="01-Feb"/>
+          <s v="02-Feb"/>
+          <s v="03-Feb"/>
+          <s v="04-Feb"/>
+          <s v="05-Feb"/>
+          <s v="06-Feb"/>
+          <s v="07-Feb"/>
+          <s v="08-Feb"/>
+          <s v="09-Feb"/>
+          <s v="10-Feb"/>
+          <s v="11-Feb"/>
+          <s v="12-Feb"/>
+          <s v="13-Feb"/>
+          <s v="14-Feb"/>
+          <s v="15-Feb"/>
+          <s v="16-Feb"/>
+          <s v="17-Feb"/>
+          <s v="18-Feb"/>
+          <s v="19-Feb"/>
+          <s v="20-Feb"/>
+          <s v="21-Feb"/>
+          <s v="22-Feb"/>
+          <s v="23-Feb"/>
+          <s v="24-Feb"/>
+          <s v="25-Feb"/>
+          <s v="26-Feb"/>
+          <s v="27-Feb"/>
+          <s v="28-Feb"/>
+          <s v="29-Feb"/>
+          <s v="01-Mar"/>
+          <s v="02-Mar"/>
+          <s v="03-Mar"/>
+          <s v="04-Mar"/>
+          <s v="05-Mar"/>
+          <s v="06-Mar"/>
+          <s v="07-Mar"/>
+          <s v="08-Mar"/>
+          <s v="09-Mar"/>
+          <s v="10-Mar"/>
+          <s v="11-Mar"/>
+          <s v="12-Mar"/>
+          <s v="13-Mar"/>
+          <s v="14-Mar"/>
+          <s v="15-Mar"/>
+          <s v="16-Mar"/>
+          <s v="17-Mar"/>
+          <s v="18-Mar"/>
+          <s v="19-Mar"/>
+          <s v="20-Mar"/>
+          <s v="21-Mar"/>
+          <s v="22-Mar"/>
+          <s v="23-Mar"/>
+          <s v="24-Mar"/>
+          <s v="25-Mar"/>
+          <s v="26-Mar"/>
+          <s v="27-Mar"/>
+          <s v="28-Mar"/>
+          <s v="29-Mar"/>
+          <s v="30-Mar"/>
+          <s v="31-Mar"/>
+          <s v="01-Apr"/>
+          <s v="02-Apr"/>
+          <s v="03-Apr"/>
+          <s v="04-Apr"/>
+          <s v="05-Apr"/>
+          <s v="06-Apr"/>
+          <s v="07-Apr"/>
+          <s v="08-Apr"/>
+          <s v="09-Apr"/>
+          <s v="10-Apr"/>
+          <s v="11-Apr"/>
+          <s v="12-Apr"/>
+          <s v="13-Apr"/>
+          <s v="14-Apr"/>
+          <s v="15-Apr"/>
+          <s v="16-Apr"/>
+          <s v="17-Apr"/>
+          <s v="18-Apr"/>
+          <s v="19-Apr"/>
+          <s v="20-Apr"/>
+          <s v="21-Apr"/>
+          <s v="22-Apr"/>
+          <s v="23-Apr"/>
+          <s v="24-Apr"/>
+          <s v="25-Apr"/>
+          <s v="26-Apr"/>
+          <s v="27-Apr"/>
+          <s v="28-Apr"/>
+          <s v="29-Apr"/>
+          <s v="30-Apr"/>
+          <s v="01-May"/>
+          <s v="02-May"/>
+          <s v="03-May"/>
+          <s v="04-May"/>
+          <s v="05-May"/>
+          <s v="06-May"/>
+          <s v="07-May"/>
+          <s v="08-May"/>
+          <s v="09-May"/>
+          <s v="10-May"/>
+          <s v="11-May"/>
+          <s v="12-May"/>
+          <s v="13-May"/>
+          <s v="14-May"/>
+          <s v="15-May"/>
+          <s v="16-May"/>
+          <s v="17-May"/>
+          <s v="18-May"/>
+          <s v="19-May"/>
+          <s v="20-May"/>
+          <s v="21-May"/>
+          <s v="22-May"/>
+          <s v="23-May"/>
+          <s v="24-May"/>
+          <s v="25-May"/>
+          <s v="26-May"/>
+          <s v="27-May"/>
+          <s v="28-May"/>
+          <s v="29-May"/>
+          <s v="30-May"/>
+          <s v="31-May"/>
+          <s v="01-Jun"/>
+          <s v="02-Jun"/>
+          <s v="03-Jun"/>
+          <s v="04-Jun"/>
+          <s v="05-Jun"/>
+          <s v="06-Jun"/>
+          <s v="07-Jun"/>
+          <s v="08-Jun"/>
+          <s v="09-Jun"/>
+          <s v="10-Jun"/>
+          <s v="11-Jun"/>
+          <s v="12-Jun"/>
+          <s v="13-Jun"/>
+          <s v="14-Jun"/>
+          <s v="15-Jun"/>
+          <s v="16-Jun"/>
+          <s v="17-Jun"/>
+          <s v="18-Jun"/>
+          <s v="19-Jun"/>
+          <s v="20-Jun"/>
+          <s v="21-Jun"/>
+          <s v="22-Jun"/>
+          <s v="23-Jun"/>
+          <s v="24-Jun"/>
+          <s v="25-Jun"/>
+          <s v="26-Jun"/>
+          <s v="27-Jun"/>
+          <s v="28-Jun"/>
+          <s v="29-Jun"/>
+          <s v="30-Jun"/>
+          <s v="01-Jul"/>
+          <s v="02-Jul"/>
+          <s v="03-Jul"/>
+          <s v="04-Jul"/>
+          <s v="05-Jul"/>
+          <s v="06-Jul"/>
+          <s v="07-Jul"/>
+          <s v="08-Jul"/>
+          <s v="09-Jul"/>
+          <s v="10-Jul"/>
+          <s v="11-Jul"/>
+          <s v="12-Jul"/>
+          <s v="13-Jul"/>
+          <s v="14-Jul"/>
+          <s v="15-Jul"/>
+          <s v="16-Jul"/>
+          <s v="17-Jul"/>
+          <s v="18-Jul"/>
+          <s v="19-Jul"/>
+          <s v="20-Jul"/>
+          <s v="21-Jul"/>
+          <s v="22-Jul"/>
+          <s v="23-Jul"/>
+          <s v="24-Jul"/>
+          <s v="25-Jul"/>
+          <s v="26-Jul"/>
+          <s v="27-Jul"/>
+          <s v="28-Jul"/>
+          <s v="29-Jul"/>
+          <s v="30-Jul"/>
+          <s v="31-Jul"/>
+          <s v="01-Aug"/>
+          <s v="02-Aug"/>
+          <s v="03-Aug"/>
+          <s v="04-Aug"/>
+          <s v="05-Aug"/>
+          <s v="06-Aug"/>
+          <s v="07-Aug"/>
+          <s v="08-Aug"/>
+          <s v="09-Aug"/>
+          <s v="10-Aug"/>
+          <s v="11-Aug"/>
+          <s v="12-Aug"/>
+          <s v="13-Aug"/>
+          <s v="14-Aug"/>
+          <s v="15-Aug"/>
+          <s v="16-Aug"/>
+          <s v="17-Aug"/>
+          <s v="18-Aug"/>
+          <s v="19-Aug"/>
+          <s v="20-Aug"/>
+          <s v="21-Aug"/>
+          <s v="22-Aug"/>
+          <s v="23-Aug"/>
+          <s v="24-Aug"/>
+          <s v="25-Aug"/>
+          <s v="26-Aug"/>
+          <s v="27-Aug"/>
+          <s v="28-Aug"/>
+          <s v="29-Aug"/>
+          <s v="30-Aug"/>
+          <s v="31-Aug"/>
+          <s v="01-Sep"/>
+          <s v="02-Sep"/>
+          <s v="03-Sep"/>
+          <s v="04-Sep"/>
+          <s v="05-Sep"/>
+          <s v="06-Sep"/>
+          <s v="07-Sep"/>
+          <s v="08-Sep"/>
+          <s v="09-Sep"/>
+          <s v="10-Sep"/>
+          <s v="11-Sep"/>
+          <s v="12-Sep"/>
+          <s v="13-Sep"/>
+          <s v="14-Sep"/>
+          <s v="15-Sep"/>
+          <s v="16-Sep"/>
+          <s v="17-Sep"/>
+          <s v="18-Sep"/>
+          <s v="19-Sep"/>
+          <s v="20-Sep"/>
+          <s v="21-Sep"/>
+          <s v="22-Sep"/>
+          <s v="23-Sep"/>
+          <s v="24-Sep"/>
+          <s v="25-Sep"/>
+          <s v="26-Sep"/>
+          <s v="27-Sep"/>
+          <s v="28-Sep"/>
+          <s v="29-Sep"/>
+          <s v="30-Sep"/>
+          <s v="01-Oct"/>
+          <s v="02-Oct"/>
+          <s v="03-Oct"/>
+          <s v="04-Oct"/>
+          <s v="05-Oct"/>
+          <s v="06-Oct"/>
+          <s v="07-Oct"/>
+          <s v="08-Oct"/>
+          <s v="09-Oct"/>
+          <s v="10-Oct"/>
+          <s v="11-Oct"/>
+          <s v="12-Oct"/>
+          <s v="13-Oct"/>
+          <s v="14-Oct"/>
+          <s v="15-Oct"/>
+          <s v="16-Oct"/>
+          <s v="17-Oct"/>
+          <s v="18-Oct"/>
+          <s v="19-Oct"/>
+          <s v="20-Oct"/>
+          <s v="21-Oct"/>
+          <s v="22-Oct"/>
+          <s v="23-Oct"/>
+          <s v="24-Oct"/>
+          <s v="25-Oct"/>
+          <s v="26-Oct"/>
+          <s v="27-Oct"/>
+          <s v="28-Oct"/>
+          <s v="29-Oct"/>
+          <s v="30-Oct"/>
+          <s v="31-Oct"/>
+          <s v="01-Nov"/>
+          <s v="02-Nov"/>
+          <s v="03-Nov"/>
+          <s v="04-Nov"/>
+          <s v="05-Nov"/>
+          <s v="06-Nov"/>
+          <s v="07-Nov"/>
+          <s v="08-Nov"/>
+          <s v="09-Nov"/>
+          <s v="10-Nov"/>
+          <s v="11-Nov"/>
+          <s v="12-Nov"/>
+          <s v="13-Nov"/>
+          <s v="14-Nov"/>
+          <s v="15-Nov"/>
+          <s v="16-Nov"/>
+          <s v="17-Nov"/>
+          <s v="18-Nov"/>
+          <s v="19-Nov"/>
+          <s v="20-Nov"/>
+          <s v="21-Nov"/>
+          <s v="22-Nov"/>
+          <s v="23-Nov"/>
+          <s v="24-Nov"/>
+          <s v="25-Nov"/>
+          <s v="26-Nov"/>
+          <s v="27-Nov"/>
+          <s v="28-Nov"/>
+          <s v="29-Nov"/>
+          <s v="30-Nov"/>
+          <s v="01-Dec"/>
+          <s v="02-Dec"/>
+          <s v="03-Dec"/>
+          <s v="04-Dec"/>
+          <s v="05-Dec"/>
+          <s v="06-Dec"/>
+          <s v="07-Dec"/>
+          <s v="08-Dec"/>
+          <s v="09-Dec"/>
+          <s v="10-Dec"/>
+          <s v="11-Dec"/>
+          <s v="12-Dec"/>
+          <s v="13-Dec"/>
+          <s v="14-Dec"/>
+          <s v="15-Dec"/>
+          <s v="16-Dec"/>
+          <s v="17-Dec"/>
+          <s v="18-Dec"/>
+          <s v="19-Dec"/>
+          <s v="20-Dec"/>
+          <s v="21-Dec"/>
+          <s v="22-Dec"/>
+          <s v="23-Dec"/>
+          <s v="24-Dec"/>
+          <s v="25-Dec"/>
+          <s v="26-Dec"/>
+          <s v="27-Dec"/>
+          <s v="28-Dec"/>
+          <s v="29-Dec"/>
+          <s v="30-Dec"/>
+          <s v="31-Dec"/>
+          <s v="&gt;14-02-2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Months (Date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="months" startDate="2026-01-01T00:00:00" endDate="2026-02-14T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;01-01-2026"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;14-02-2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="626928714"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="44">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Internship"/>
+    <n v="15000"/>
+    <x v="0"/>
+    <s v="Bank"/>
+    <s v="Money In"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="250"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Uber"/>
+    <n v="180"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Electricity"/>
+    <n v="1200"/>
+    <x v="1"/>
+    <s v="Bank"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Netflix"/>
+    <n v="499"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <s v="Clothes"/>
+    <n v="2000"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="300"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <s v="Bus"/>
+    <n v="50"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <s v="Groceries"/>
+    <n v="1200"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="0"/>
+    <s v="Freelance"/>
+    <n v="5000"/>
+    <x v="0"/>
+    <s v="Bank"/>
+    <s v="Money In"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="3"/>
+    <s v="Internet"/>
+    <n v="800"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="4"/>
+    <s v="Movie"/>
+    <n v="300"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="220"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="5"/>
+    <s v="Amazon"/>
+    <n v="1500"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="2"/>
+    <s v="Auto"/>
+    <n v="100"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="270"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="3"/>
+    <s v="Mobile Recharge"/>
+    <n v="399"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="4"/>
+    <s v="Spotify"/>
+    <n v="119"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="5"/>
+    <s v="Shoes"/>
+    <n v="2500"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="2"/>
+    <s v="Uber"/>
+    <n v="200"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="1"/>
+    <s v="Groceries"/>
+    <n v="1000"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="0"/>
+    <s v="Part-time"/>
+    <n v="4000"/>
+    <x v="0"/>
+    <s v="Bank"/>
+    <s v="Money In"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="3"/>
+    <s v="Water"/>
+    <n v="300"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="4"/>
+    <s v="Game"/>
+    <n v="600"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="260"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="5"/>
+    <s v="Accessories"/>
+    <n v="800"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="2"/>
+    <s v="Metro"/>
+    <n v="150"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="320"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="3"/>
+    <s v="Gas"/>
+    <n v="700"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="4"/>
+    <s v="Movie"/>
+    <n v="350"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="1"/>
+    <s v="Groceries"/>
+    <n v="1300"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="0"/>
+    <s v="Internship"/>
+    <n v="15000"/>
+    <x v="0"/>
+    <s v="Bank"/>
+    <s v="Money In"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="240"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="2"/>
+    <s v="Uber"/>
+    <n v="190"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="3"/>
+    <s v="Electricity"/>
+    <n v="1100"/>
+    <x v="1"/>
+    <s v="Bank"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="4"/>
+    <s v="Netflix"/>
+    <n v="499"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="5"/>
+    <s v="Clothes"/>
+    <n v="1800"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="1"/>
+    <s v="Zomato"/>
+    <n v="310"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="2"/>
+    <s v="Bus"/>
+    <n v="60"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="1"/>
+    <s v="Groceries"/>
+    <n v="1100"/>
+    <x v="1"/>
+    <s v="Card"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="0"/>
+    <s v="Freelance"/>
+    <n v="4500"/>
+    <x v="0"/>
+    <s v="Bank"/>
+    <s v="Money In"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="3"/>
+    <s v="Internet"/>
+    <n v="800"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <x v="4"/>
+    <s v="Movie"/>
+    <n v="320"/>
+    <x v="1"/>
+    <s v="Cash"/>
+    <s v="Money Out"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <x v="1"/>
+    <s v="Swiggy"/>
+    <n v="230"/>
+    <x v="1"/>
+    <s v="UPI"/>
+    <s v="Money Out"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E6E8893-F1A8-42E5-99A6-475256BBE3D5}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField numFmtId="16" showAll="0">
+      <items count="45">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="13" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8230E6C-0CD5-48EC-8C19-ECD7D4C25770}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField numFmtId="16" showAll="0">
+      <items count="45">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{19D3993E-4445-48C0-8B13-BC6A432E292C}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="A3:D7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" numFmtId="16" showAll="0" measureFilter="1">
+      <items count="45">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="8"/>
+    <field x="7"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="13" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Months__Date" xr10:uid="{900F6F85-D112-407B-9D4B-9710AF33B1EE}" sourceName="Months (Date)">
+  <pivotTables>
+    <pivotTable tabId="2" name="PivotTable1"/>
+    <pivotTable tabId="3" name="PivotTable2"/>
+    <pivotTable tabId="4" name="PivotTable3"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="626928714">
+      <items count="14">
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1" nd="1"/>
+        <i x="4" s="1" nd="1"/>
+        <i x="5" s="1" nd="1"/>
+        <i x="6" s="1" nd="1"/>
+        <i x="7" s="1" nd="1"/>
+        <i x="8" s="1" nd="1"/>
+        <i x="9" s="1" nd="1"/>
+        <i x="10" s="1" nd="1"/>
+        <i x="11" s="1" nd="1"/>
+        <i x="12" s="1" nd="1"/>
+        <i x="0" s="1" nd="1"/>
+        <i x="13" s="1" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{470722E0-AACD-4C17-9CDC-17EF765DBC7E}">
+      <x15:slicerCacheHideItemsWithNoData/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Category" xr10:uid="{098C1E2D-DD86-45AC-BCB6-77E1AA7C452A}" sourceName="Category">
+  <pivotTables>
+    <pivotTable tabId="2" name="PivotTable1"/>
+    <pivotTable tabId="3" name="PivotTable2"/>
+    <pivotTable tabId="4" name="PivotTable3"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="626928714">
+      <items count="6">
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="5" s="1"/>
+        <i x="2" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Months (Date) 1" xr10:uid="{B655CC54-5176-486B-99A0-9C7B63F9A94B}" cache="Slicer_Months__Date" caption="Months (Date)" columnCount="2" rowHeight="1188000"/>
+  <slicer name="Category 1" xr10:uid="{76485937-7C22-4C20-9936-811D9FD8F5FB}" cache="Slicer_Category" caption="Category" columnCount="3" style="SlicerStyleDark6" rowHeight="612000"/>
+</slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1603,4 +7227,419 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{278AA136-8966-45CA-AFE3-E55B391668A0}">
+  <dimension ref="A3:B10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5">
+        <v>5299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="5">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="5">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="5">
+        <v>68016</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EE7C936-D7F4-4D63-8187-1D66377F8BC9}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5">
+        <v>24516</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5">
+        <v>68016</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65EE625-60DE-498A-ACD1-B7047B234720}">
+  <dimension ref="A3:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="5">
+        <v>17867</v>
+      </c>
+      <c r="C5" s="5">
+        <v>24000</v>
+      </c>
+      <c r="D5" s="5">
+        <v>41867</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="5">
+        <v>6649</v>
+      </c>
+      <c r="C6" s="5">
+        <v>19500</v>
+      </c>
+      <c r="D6" s="5">
+        <v>26149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="5">
+        <v>24516</v>
+      </c>
+      <c r="C7" s="5">
+        <v>43500</v>
+      </c>
+      <c r="D7" s="5">
+        <v>68016</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0215578A-5192-43CB-AA5E-050017F26830}">
+  <dimension ref="E5:AE15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="17.21875" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="18" max="18" width="9.6640625" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="22" max="22" width="22.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="5:31" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="15"/>
+    </row>
+    <row r="6" spans="5:31" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="18"/>
+    </row>
+    <row r="7" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="E7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="21"/>
+    </row>
+    <row r="8" spans="5:31" ht="19.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="V8" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="W8" s="23">
+        <f>GETPIVOTDATA("Amount",PivotTable2!$A$3,"Type","Income")</f>
+        <v>43500</v>
+      </c>
+      <c r="X8" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+    </row>
+    <row r="9" spans="5:31" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="V9" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="W9" s="23">
+        <f>GETPIVOTDATA("Amount",PivotTable2!$A$3,"Type","Expense")</f>
+        <v>24516</v>
+      </c>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+    </row>
+    <row r="10" spans="5:31" ht="19.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="V10" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="W10" s="23">
+        <f>W8-W9</f>
+        <v>18984</v>
+      </c>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+    </row>
+    <row r="11" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="V11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="12"/>
+    </row>
+    <row r="12" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="V12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="9"/>
+    </row>
+    <row r="13" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="J13" s="6"/>
+      <c r="V13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="9"/>
+    </row>
+    <row r="14" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="V14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="9"/>
+    </row>
+    <row r="15" spans="5:31" x14ac:dyDescent="0.3">
+      <c r="V15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="8"/>
+      <c r="AD15" s="8"/>
+      <c r="AE15" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="E5:S7"/>
+    <mergeCell ref="V11:AE11"/>
+    <mergeCell ref="V12:AE12"/>
+    <mergeCell ref="V13:AE13"/>
+    <mergeCell ref="V14:AE14"/>
+    <mergeCell ref="V15:AE15"/>
+    <mergeCell ref="X8:AE10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
 </file>